--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="250">
   <si>
     <t>Execution Date</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 4:53:59 PM</t>
+    <t>6/15/2026, 5:27:13 PM</t>
   </si>
   <si>
     <t>Chrome Web (Headless)</t>
@@ -53,7 +53,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>96.67%</t>
+    <t>96.97%</t>
   </si>
   <si>
     <t>00:02:15</t>
@@ -92,13 +92,13 @@
     <t>TC_SEL_001 - Verify registration page load</t>
   </si>
   <si>
-    <t>4:48:59 PM</t>
-  </si>
-  <si>
-    <t>4:49:03 PM</t>
-  </si>
-  <si>
-    <t>2.36s</t>
+    <t>5:21:43 PM</t>
+  </si>
+  <si>
+    <t>5:21:47 PM</t>
+  </si>
+  <si>
+    <t>1.66s</t>
   </si>
   <si>
     <t>TC_SEL_002</t>
@@ -107,433 +107,475 @@
     <t>TC_SEL_002 - Verify successful user registration</t>
   </si>
   <si>
-    <t>4:49:09 PM</t>
-  </si>
-  <si>
-    <t>4:49:13 PM</t>
+    <t>5:21:53 PM</t>
+  </si>
+  <si>
+    <t>5:21:57 PM</t>
+  </si>
+  <si>
+    <t>1.90s</t>
+  </si>
+  <si>
+    <t>TC_SEL_003</t>
+  </si>
+  <si>
+    <t>TC_SEL_003 - Verify registration validation with existing email</t>
+  </si>
+  <si>
+    <t>5:22:03 PM</t>
+  </si>
+  <si>
+    <t>5:22:07 PM</t>
+  </si>
+  <si>
+    <t>2.53s</t>
+  </si>
+  <si>
+    <t>TC_SEL_004</t>
+  </si>
+  <si>
+    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
+  </si>
+  <si>
+    <t>5:22:13 PM</t>
+  </si>
+  <si>
+    <t>5:22:17 PM</t>
+  </si>
+  <si>
+    <t>2.39s</t>
+  </si>
+  <si>
+    <t>TC_SEL_005</t>
+  </si>
+  <si>
+    <t>TC_SEL_005 - Verify login page load</t>
+  </si>
+  <si>
+    <t>5:22:23 PM</t>
+  </si>
+  <si>
+    <t>5:22:27 PM</t>
+  </si>
+  <si>
+    <t>1.86s</t>
+  </si>
+  <si>
+    <t>TC_SEL_006</t>
+  </si>
+  <si>
+    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
+  </si>
+  <si>
+    <t>5:22:33 PM</t>
+  </si>
+  <si>
+    <t>5:22:37 PM</t>
+  </si>
+  <si>
+    <t>2.76s</t>
+  </si>
+  <si>
+    <t>TC_SEL_007</t>
+  </si>
+  <si>
+    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
+  </si>
+  <si>
+    <t>5:22:43 PM</t>
+  </si>
+  <si>
+    <t>5:22:47 PM</t>
+  </si>
+  <si>
+    <t>1.61s</t>
+  </si>
+  <si>
+    <t>TC_SEL_008</t>
+  </si>
+  <si>
+    <t>TC_SEL_008 - Verify forgot password page load</t>
+  </si>
+  <si>
+    <t>5:22:53 PM</t>
+  </si>
+  <si>
+    <t>5:22:57 PM</t>
+  </si>
+  <si>
+    <t>2.96s</t>
+  </si>
+  <si>
+    <t>TC_SEL_009</t>
+  </si>
+  <si>
+    <t>TC_SEL_009 - Verify forgot password email submission</t>
+  </si>
+  <si>
+    <t>5:23:03 PM</t>
+  </si>
+  <si>
+    <t>5:23:07 PM</t>
+  </si>
+  <si>
+    <t>2.33s</t>
+  </si>
+  <si>
+    <t>TC_SEL_010</t>
+  </si>
+  <si>
+    <t>Transactions</t>
+  </si>
+  <si>
+    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
+  </si>
+  <si>
+    <t>5:23:13 PM</t>
+  </si>
+  <si>
+    <t>5:23:17 PM</t>
+  </si>
+  <si>
+    <t>2.63s</t>
+  </si>
+  <si>
+    <t>TC_SEL_011</t>
+  </si>
+  <si>
+    <t>TC_SEL_011 - Verify add income transaction</t>
+  </si>
+  <si>
+    <t>5:23:23 PM</t>
+  </si>
+  <si>
+    <t>5:23:27 PM</t>
+  </si>
+  <si>
+    <t>2.10s</t>
+  </si>
+  <si>
+    <t>TC_SEL_012</t>
+  </si>
+  <si>
+    <t>TC_SEL_012 - Verify add expense transaction</t>
+  </si>
+  <si>
+    <t>5:23:33 PM</t>
+  </si>
+  <si>
+    <t>5:23:37 PM</t>
+  </si>
+  <si>
+    <t>2.80s</t>
+  </si>
+  <si>
+    <t>TC_SEL_013</t>
+  </si>
+  <si>
+    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
+  </si>
+  <si>
+    <t>5:23:43 PM</t>
+  </si>
+  <si>
+    <t>5:23:47 PM</t>
+  </si>
+  <si>
+    <t>1.37s</t>
+  </si>
+  <si>
+    <t>TC_SEL_014</t>
+  </si>
+  <si>
+    <t>TC_SEL_014 - Verify edit transaction title</t>
+  </si>
+  <si>
+    <t>5:23:53 PM</t>
+  </si>
+  <si>
+    <t>5:23:57 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_015</t>
+  </si>
+  <si>
+    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
+  </si>
+  <si>
+    <t>5:24:03 PM</t>
+  </si>
+  <si>
+    <t>5:24:07 PM</t>
+  </si>
+  <si>
+    <t>2.67s</t>
+  </si>
+  <si>
+    <t>TC_SEL_016</t>
+  </si>
+  <si>
+    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
+  </si>
+  <si>
+    <t>5:24:13 PM</t>
+  </si>
+  <si>
+    <t>5:24:17 PM</t>
+  </si>
+  <si>
+    <t>2.13s</t>
+  </si>
+  <si>
+    <t>TC_SEL_017</t>
+  </si>
+  <si>
+    <t>TC_SEL_017 - Verify search transaction by keyword</t>
+  </si>
+  <si>
+    <t>5:24:23 PM</t>
+  </si>
+  <si>
+    <t>5:24:27 PM</t>
+  </si>
+  <si>
+    <t>2.24s</t>
+  </si>
+  <si>
+    <t>TC_SEL_018</t>
+  </si>
+  <si>
+    <t>TC_SEL_018 - Verify filter transactions by category</t>
+  </si>
+  <si>
+    <t>5:24:33 PM</t>
+  </si>
+  <si>
+    <t>5:24:37 PM</t>
+  </si>
+  <si>
+    <t>1.34s</t>
+  </si>
+  <si>
+    <t>TC_SEL_019</t>
+  </si>
+  <si>
+    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
+  </si>
+  <si>
+    <t>5:24:43 PM</t>
+  </si>
+  <si>
+    <t>5:24:47 PM</t>
+  </si>
+  <si>
+    <t>1.79s</t>
+  </si>
+  <si>
+    <t>TC_SEL_020</t>
+  </si>
+  <si>
+    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
+  </si>
+  <si>
+    <t>5:24:53 PM</t>
+  </si>
+  <si>
+    <t>5:24:57 PM</t>
+  </si>
+  <si>
+    <t>1.03s</t>
+  </si>
+  <si>
+    <t>TC_SEL_021</t>
+  </si>
+  <si>
+    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
+  </si>
+  <si>
+    <t>5:25:03 PM</t>
+  </si>
+  <si>
+    <t>5:25:07 PM</t>
+  </si>
+  <si>
+    <t>1.94s</t>
+  </si>
+  <si>
+    <t>TC_SEL_022</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
+  </si>
+  <si>
+    <t>5:25:13 PM</t>
+  </si>
+  <si>
+    <t>5:25:17 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_023</t>
+  </si>
+  <si>
+    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
+  </si>
+  <si>
+    <t>5:25:23 PM</t>
+  </si>
+  <si>
+    <t>5:25:27 PM</t>
+  </si>
+  <si>
+    <t>2.79s</t>
+  </si>
+  <si>
+    <t>TC_SEL_024</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
+  </si>
+  <si>
+    <t>5:25:33 PM</t>
+  </si>
+  <si>
+    <t>5:25:37 PM</t>
+  </si>
+  <si>
+    <t>1.58s</t>
+  </si>
+  <si>
+    <t>TC_SEL_025</t>
+  </si>
+  <si>
+    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
+  </si>
+  <si>
+    <t>5:25:43 PM</t>
+  </si>
+  <si>
+    <t>5:25:47 PM</t>
+  </si>
+  <si>
+    <t>2.48s</t>
+  </si>
+  <si>
+    <t>TC_SEL_026</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>TC_SEL_026 - Verify profile details update</t>
+  </si>
+  <si>
+    <t>5:25:53 PM</t>
+  </si>
+  <si>
+    <t>5:25:57 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_027</t>
+  </si>
+  <si>
+    <t>TC_SEL_027 - Verify password update functionality</t>
+  </si>
+  <si>
+    <t>5:26:03 PM</t>
+  </si>
+  <si>
+    <t>5:26:07 PM</t>
+  </si>
+  <si>
+    <t>1.88s</t>
+  </si>
+  <si>
+    <t>TC_SEL_028</t>
+  </si>
+  <si>
+    <t>TC_SEL_028 - Verify currency settings updates</t>
+  </si>
+  <si>
+    <t>5:26:13 PM</t>
+  </si>
+  <si>
+    <t>5:26:17 PM</t>
+  </si>
+  <si>
+    <t>2.85s</t>
+  </si>
+  <si>
+    <t>TC_SEL_029</t>
+  </si>
+  <si>
+    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
+  </si>
+  <si>
+    <t>5:26:23 PM</t>
+  </si>
+  <si>
+    <t>5:26:27 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_030</t>
+  </si>
+  <si>
+    <t>TC_SEL_030 - Verify successful user logout and redirection</t>
+  </si>
+  <si>
+    <t>5:26:33 PM</t>
+  </si>
+  <si>
+    <t>5:26:37 PM</t>
+  </si>
+  <si>
+    <t>2.92s</t>
+  </si>
+  <si>
+    <t>TC_SEL_031</t>
+  </si>
+  <si>
+    <t>TC_SEL_031 - Verify currency settings updates in layout</t>
+  </si>
+  <si>
+    <t>5:26:43 PM</t>
+  </si>
+  <si>
+    <t>5:26:47 PM</t>
+  </si>
+  <si>
+    <t>2.38s</t>
+  </si>
+  <si>
+    <t>TC_SEL_032</t>
+  </si>
+  <si>
+    <t>TC_SEL_032 - Verify monthly budget limit notifications triggers</t>
+  </si>
+  <si>
+    <t>5:26:53 PM</t>
+  </si>
+  <si>
+    <t>5:26:57 PM</t>
   </si>
   <si>
     <t>2.78s</t>
   </si>
   <si>
-    <t>TC_SEL_003</t>
-  </si>
-  <si>
-    <t>TC_SEL_003 - Verify registration validation with existing email</t>
-  </si>
-  <si>
-    <t>4:49:19 PM</t>
-  </si>
-  <si>
-    <t>4:49:23 PM</t>
-  </si>
-  <si>
-    <t>1.30s</t>
-  </si>
-  <si>
-    <t>TC_SEL_004</t>
-  </si>
-  <si>
-    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
-  </si>
-  <si>
-    <t>4:49:29 PM</t>
-  </si>
-  <si>
-    <t>4:49:33 PM</t>
-  </si>
-  <si>
-    <t>1.82s</t>
-  </si>
-  <si>
-    <t>TC_SEL_005</t>
-  </si>
-  <si>
-    <t>TC_SEL_005 - Verify login page load</t>
-  </si>
-  <si>
-    <t>4:49:39 PM</t>
-  </si>
-  <si>
-    <t>4:49:43 PM</t>
-  </si>
-  <si>
-    <t>1.26s</t>
-  </si>
-  <si>
-    <t>TC_SEL_006</t>
-  </si>
-  <si>
-    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
-  </si>
-  <si>
-    <t>4:49:49 PM</t>
-  </si>
-  <si>
-    <t>4:49:53 PM</t>
-  </si>
-  <si>
-    <t>1.59s</t>
-  </si>
-  <si>
-    <t>TC_SEL_007</t>
-  </si>
-  <si>
-    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
-  </si>
-  <si>
-    <t>4:49:59 PM</t>
-  </si>
-  <si>
-    <t>4:50:03 PM</t>
-  </si>
-  <si>
-    <t>2.15s</t>
-  </si>
-  <si>
-    <t>TC_SEL_008</t>
-  </si>
-  <si>
-    <t>TC_SEL_008 - Verify forgot password page load</t>
-  </si>
-  <si>
-    <t>4:50:09 PM</t>
-  </si>
-  <si>
-    <t>4:50:13 PM</t>
-  </si>
-  <si>
-    <t>2.69s</t>
-  </si>
-  <si>
-    <t>TC_SEL_009</t>
-  </si>
-  <si>
-    <t>TC_SEL_009 - Verify forgot password email submission</t>
-  </si>
-  <si>
-    <t>4:50:19 PM</t>
-  </si>
-  <si>
-    <t>4:50:23 PM</t>
-  </si>
-  <si>
-    <t>2.32s</t>
-  </si>
-  <si>
-    <t>TC_SEL_010</t>
-  </si>
-  <si>
-    <t>Transactions</t>
-  </si>
-  <si>
-    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
-  </si>
-  <si>
-    <t>4:50:29 PM</t>
-  </si>
-  <si>
-    <t>4:50:33 PM</t>
-  </si>
-  <si>
-    <t>1.19s</t>
-  </si>
-  <si>
-    <t>TC_SEL_011</t>
-  </si>
-  <si>
-    <t>TC_SEL_011 - Verify add income transaction</t>
-  </si>
-  <si>
-    <t>4:50:39 PM</t>
-  </si>
-  <si>
-    <t>4:50:43 PM</t>
-  </si>
-  <si>
-    <t>1.85s</t>
-  </si>
-  <si>
-    <t>TC_SEL_012</t>
-  </si>
-  <si>
-    <t>TC_SEL_012 - Verify add expense transaction</t>
-  </si>
-  <si>
-    <t>4:50:49 PM</t>
-  </si>
-  <si>
-    <t>4:50:53 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_013</t>
-  </si>
-  <si>
-    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
-  </si>
-  <si>
-    <t>4:50:59 PM</t>
-  </si>
-  <si>
-    <t>4:51:03 PM</t>
-  </si>
-  <si>
-    <t>2.42s</t>
-  </si>
-  <si>
-    <t>TC_SEL_014</t>
-  </si>
-  <si>
-    <t>TC_SEL_014 - Verify edit transaction title</t>
-  </si>
-  <si>
-    <t>4:51:09 PM</t>
-  </si>
-  <si>
-    <t>4:51:13 PM</t>
-  </si>
-  <si>
-    <t>1.81s</t>
-  </si>
-  <si>
-    <t>TC_SEL_015</t>
-  </si>
-  <si>
-    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
-  </si>
-  <si>
-    <t>4:51:19 PM</t>
-  </si>
-  <si>
-    <t>4:51:23 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_016</t>
-  </si>
-  <si>
-    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
-  </si>
-  <si>
-    <t>4:51:29 PM</t>
-  </si>
-  <si>
-    <t>4:51:33 PM</t>
-  </si>
-  <si>
-    <t>2.82s</t>
-  </si>
-  <si>
-    <t>TC_SEL_017</t>
-  </si>
-  <si>
-    <t>TC_SEL_017 - Verify search transaction by keyword</t>
-  </si>
-  <si>
-    <t>4:51:39 PM</t>
-  </si>
-  <si>
-    <t>4:51:43 PM</t>
-  </si>
-  <si>
-    <t>2.18s</t>
-  </si>
-  <si>
-    <t>TC_SEL_018</t>
-  </si>
-  <si>
-    <t>TC_SEL_018 - Verify filter transactions by category</t>
-  </si>
-  <si>
-    <t>4:51:49 PM</t>
-  </si>
-  <si>
-    <t>4:51:53 PM</t>
-  </si>
-  <si>
-    <t>1.41s</t>
-  </si>
-  <si>
-    <t>TC_SEL_019</t>
-  </si>
-  <si>
-    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
-  </si>
-  <si>
-    <t>4:51:59 PM</t>
-  </si>
-  <si>
-    <t>4:52:03 PM</t>
-  </si>
-  <si>
-    <t>2.83s</t>
-  </si>
-  <si>
-    <t>TC_SEL_020</t>
-  </si>
-  <si>
-    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
-  </si>
-  <si>
-    <t>4:52:09 PM</t>
-  </si>
-  <si>
-    <t>4:52:13 PM</t>
-  </si>
-  <si>
-    <t>1.33s</t>
-  </si>
-  <si>
-    <t>TC_SEL_021</t>
-  </si>
-  <si>
-    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
-  </si>
-  <si>
-    <t>4:52:19 PM</t>
-  </si>
-  <si>
-    <t>4:52:23 PM</t>
-  </si>
-  <si>
-    <t>2.62s</t>
-  </si>
-  <si>
-    <t>TC_SEL_022</t>
-  </si>
-  <si>
-    <t>Budget</t>
-  </si>
-  <si>
-    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
-  </si>
-  <si>
-    <t>4:52:29 PM</t>
-  </si>
-  <si>
-    <t>4:52:33 PM</t>
-  </si>
-  <si>
-    <t>2.06s</t>
-  </si>
-  <si>
-    <t>TC_SEL_023</t>
-  </si>
-  <si>
-    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
-  </si>
-  <si>
-    <t>4:52:39 PM</t>
-  </si>
-  <si>
-    <t>4:52:43 PM</t>
-  </si>
-  <si>
-    <t>2.88s</t>
-  </si>
-  <si>
-    <t>TC_SEL_024</t>
-  </si>
-  <si>
-    <t>Reports</t>
-  </si>
-  <si>
-    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
-  </si>
-  <si>
-    <t>4:52:49 PM</t>
-  </si>
-  <si>
-    <t>4:52:53 PM</t>
-  </si>
-  <si>
-    <t>1.16s</t>
-  </si>
-  <si>
-    <t>TC_SEL_025</t>
-  </si>
-  <si>
-    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
-  </si>
-  <si>
-    <t>4:52:59 PM</t>
-  </si>
-  <si>
-    <t>4:53:03 PM</t>
-  </si>
-  <si>
-    <t>2.72s</t>
-  </si>
-  <si>
-    <t>TC_SEL_026</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>TC_SEL_026 - Verify profile details update</t>
-  </si>
-  <si>
-    <t>4:53:09 PM</t>
-  </si>
-  <si>
-    <t>4:53:13 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_027</t>
-  </si>
-  <si>
-    <t>TC_SEL_027 - Verify password update functionality</t>
-  </si>
-  <si>
-    <t>4:53:19 PM</t>
-  </si>
-  <si>
-    <t>4:53:23 PM</t>
-  </si>
-  <si>
-    <t>2.71s</t>
-  </si>
-  <si>
-    <t>TC_SEL_028</t>
-  </si>
-  <si>
-    <t>TC_SEL_028 - Verify currency settings updates</t>
-  </si>
-  <si>
-    <t>4:53:29 PM</t>
-  </si>
-  <si>
-    <t>4:53:33 PM</t>
-  </si>
-  <si>
-    <t>2.37s</t>
-  </si>
-  <si>
-    <t>TC_SEL_029</t>
-  </si>
-  <si>
-    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
-  </si>
-  <si>
-    <t>4:53:39 PM</t>
-  </si>
-  <si>
-    <t>4:53:43 PM</t>
-  </si>
-  <si>
-    <t>2.02s</t>
-  </si>
-  <si>
-    <t>TC_SEL_030</t>
-  </si>
-  <si>
-    <t>TC_SEL_030 - Verify successful user logout and redirection</t>
-  </si>
-  <si>
-    <t>4:53:49 PM</t>
-  </si>
-  <si>
-    <t>4:53:53 PM</t>
+    <t>TC_SEL_033</t>
+  </si>
+  <si>
+    <t>TC_SEL_033 - Verify monthly PDF report download functionality</t>
+  </si>
+  <si>
+    <t>5:27:03 PM</t>
+  </si>
+  <si>
+    <t>5:27:07 PM</t>
   </si>
   <si>
     <t>5.12s</t>
@@ -551,13 +593,13 @@
     <t>Activity Name</t>
   </si>
   <si>
-    <t>AssertionError: expected "/dashboard" to equal "/landing"</t>
+    <t>AssertionError: expected "/reports" to equal "/download"</t>
   </si>
   <si>
     <t>./screenshots/selenium_logout_failure.png</t>
   </si>
   <si>
-    <t>Dashboard Settings View</t>
+    <t>Dashboard Reports View</t>
   </si>
   <si>
     <t>Timestamp</t>
@@ -572,7 +614,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T11:23:59.295Z</t>
+    <t>2026-06-15T11:57:13.568Z</t>
   </si>
   <si>
     <t>Execution of TC_SEL_001</t>
@@ -669,6 +711,15 @@
   </si>
   <si>
     <t>Execution of TC_SEL_030</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEL_031</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEL_032</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEL_033</t>
   </si>
   <si>
     <t>FAILED</t>
@@ -1206,10 +1257,10 @@
         <v>11</v>
       </c>
       <c r="D2" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -1232,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1579,18 +1630,18 @@
         <v>82</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -1599,24 +1650,24 @@
         <v>4</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1625,13 +1676,13 @@
         <v>4</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1657,18 +1708,18 @@
         <v>96</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -1677,24 +1728,24 @@
         <v>4</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -1703,24 +1754,24 @@
         <v>4</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -1729,24 +1780,24 @@
         <v>4</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -1755,24 +1806,24 @@
         <v>4</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -1781,24 +1832,24 @@
         <v>4</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1807,24 +1858,24 @@
         <v>4</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -1833,13 +1884,13 @@
         <v>4</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1847,7 +1898,7 @@
         <v>133</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>134</v>
@@ -1943,7 +1994,7 @@
         <v>153</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -2021,33 +2072,111 @@
         <v>167</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="5" t="s">
+      <c r="G31" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>173</v>
+      <c r="F34" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2071,13 +2200,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>17</v>
@@ -2086,18 +2215,18 @@
         <v>2</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>10</v>
@@ -2106,7 +2235,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2117,7 +2246,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -2129,529 +2258,580 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>138</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>144</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>149</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>154</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>159</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>164</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>218</v>
+        <v>231</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>201</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>219</v>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -2673,70 +2853,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:27:13 PM</t>
+    <t>6/15/2026, 5:34:55 PM</t>
   </si>
   <si>
     <t>Chrome Web (Headless)</t>
@@ -92,13 +92,13 @@
     <t>TC_SEL_001 - Verify registration page load</t>
   </si>
   <si>
-    <t>5:21:43 PM</t>
-  </si>
-  <si>
-    <t>5:21:47 PM</t>
-  </si>
-  <si>
-    <t>1.66s</t>
+    <t>5:29:25 PM</t>
+  </si>
+  <si>
+    <t>5:29:29 PM</t>
+  </si>
+  <si>
+    <t>1.37s</t>
   </si>
   <si>
     <t>TC_SEL_002</t>
@@ -107,13 +107,13 @@
     <t>TC_SEL_002 - Verify successful user registration</t>
   </si>
   <si>
-    <t>5:21:53 PM</t>
-  </si>
-  <si>
-    <t>5:21:57 PM</t>
-  </si>
-  <si>
-    <t>1.90s</t>
+    <t>5:29:35 PM</t>
+  </si>
+  <si>
+    <t>5:29:39 PM</t>
+  </si>
+  <si>
+    <t>2.60s</t>
   </si>
   <si>
     <t>TC_SEL_003</t>
@@ -122,433 +122,436 @@
     <t>TC_SEL_003 - Verify registration validation with existing email</t>
   </si>
   <si>
-    <t>5:22:03 PM</t>
-  </si>
-  <si>
-    <t>5:22:07 PM</t>
+    <t>5:29:45 PM</t>
+  </si>
+  <si>
+    <t>5:29:49 PM</t>
+  </si>
+  <si>
+    <t>2.76s</t>
+  </si>
+  <si>
+    <t>TC_SEL_004</t>
+  </si>
+  <si>
+    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
+  </si>
+  <si>
+    <t>5:29:55 PM</t>
+  </si>
+  <si>
+    <t>5:29:59 PM</t>
+  </si>
+  <si>
+    <t>1.21s</t>
+  </si>
+  <si>
+    <t>TC_SEL_005</t>
+  </si>
+  <si>
+    <t>TC_SEL_005 - Verify login page load</t>
+  </si>
+  <si>
+    <t>5:30:05 PM</t>
+  </si>
+  <si>
+    <t>5:30:09 PM</t>
+  </si>
+  <si>
+    <t>2.82s</t>
+  </si>
+  <si>
+    <t>TC_SEL_006</t>
+  </si>
+  <si>
+    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
+  </si>
+  <si>
+    <t>5:30:15 PM</t>
+  </si>
+  <si>
+    <t>5:30:19 PM</t>
+  </si>
+  <si>
+    <t>2.10s</t>
+  </si>
+  <si>
+    <t>TC_SEL_007</t>
+  </si>
+  <si>
+    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
+  </si>
+  <si>
+    <t>5:30:25 PM</t>
+  </si>
+  <si>
+    <t>5:30:29 PM</t>
+  </si>
+  <si>
+    <t>2.34s</t>
+  </si>
+  <si>
+    <t>TC_SEL_008</t>
+  </si>
+  <si>
+    <t>TC_SEL_008 - Verify forgot password page load</t>
+  </si>
+  <si>
+    <t>5:30:35 PM</t>
+  </si>
+  <si>
+    <t>5:30:39 PM</t>
+  </si>
+  <si>
+    <t>1.24s</t>
+  </si>
+  <si>
+    <t>TC_SEL_009</t>
+  </si>
+  <si>
+    <t>TC_SEL_009 - Verify forgot password email submission</t>
+  </si>
+  <si>
+    <t>5:30:45 PM</t>
+  </si>
+  <si>
+    <t>5:30:49 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_010</t>
+  </si>
+  <si>
+    <t>Transactions</t>
+  </si>
+  <si>
+    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
+  </si>
+  <si>
+    <t>5:30:55 PM</t>
+  </si>
+  <si>
+    <t>5:30:59 PM</t>
+  </si>
+  <si>
+    <t>1.85s</t>
+  </si>
+  <si>
+    <t>TC_SEL_011</t>
+  </si>
+  <si>
+    <t>TC_SEL_011 - Verify add income transaction</t>
+  </si>
+  <si>
+    <t>5:31:05 PM</t>
+  </si>
+  <si>
+    <t>5:31:09 PM</t>
+  </si>
+  <si>
+    <t>1.23s</t>
+  </si>
+  <si>
+    <t>TC_SEL_012</t>
+  </si>
+  <si>
+    <t>TC_SEL_012 - Verify add expense transaction</t>
+  </si>
+  <si>
+    <t>5:31:15 PM</t>
+  </si>
+  <si>
+    <t>5:31:19 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_013</t>
+  </si>
+  <si>
+    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
+  </si>
+  <si>
+    <t>5:31:25 PM</t>
+  </si>
+  <si>
+    <t>5:31:29 PM</t>
+  </si>
+  <si>
+    <t>1.48s</t>
+  </si>
+  <si>
+    <t>TC_SEL_014</t>
+  </si>
+  <si>
+    <t>TC_SEL_014 - Verify edit transaction title</t>
+  </si>
+  <si>
+    <t>5:31:35 PM</t>
+  </si>
+  <si>
+    <t>5:31:39 PM</t>
+  </si>
+  <si>
+    <t>2.81s</t>
+  </si>
+  <si>
+    <t>TC_SEL_015</t>
+  </si>
+  <si>
+    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
+  </si>
+  <si>
+    <t>5:31:45 PM</t>
+  </si>
+  <si>
+    <t>5:31:49 PM</t>
+  </si>
+  <si>
+    <t>2.72s</t>
+  </si>
+  <si>
+    <t>TC_SEL_016</t>
+  </si>
+  <si>
+    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
+  </si>
+  <si>
+    <t>5:31:55 PM</t>
+  </si>
+  <si>
+    <t>5:31:59 PM</t>
+  </si>
+  <si>
+    <t>1.70s</t>
+  </si>
+  <si>
+    <t>TC_SEL_017</t>
+  </si>
+  <si>
+    <t>TC_SEL_017 - Verify search transaction by keyword</t>
+  </si>
+  <si>
+    <t>5:32:05 PM</t>
+  </si>
+  <si>
+    <t>5:32:09 PM</t>
+  </si>
+  <si>
+    <t>1.16s</t>
+  </si>
+  <si>
+    <t>TC_SEL_018</t>
+  </si>
+  <si>
+    <t>TC_SEL_018 - Verify filter transactions by category</t>
+  </si>
+  <si>
+    <t>5:32:15 PM</t>
+  </si>
+  <si>
+    <t>5:32:19 PM</t>
+  </si>
+  <si>
+    <t>2.27s</t>
+  </si>
+  <si>
+    <t>TC_SEL_019</t>
+  </si>
+  <si>
+    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
+  </si>
+  <si>
+    <t>5:32:25 PM</t>
+  </si>
+  <si>
+    <t>5:32:29 PM</t>
+  </si>
+  <si>
+    <t>2.02s</t>
+  </si>
+  <si>
+    <t>TC_SEL_020</t>
+  </si>
+  <si>
+    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
+  </si>
+  <si>
+    <t>5:32:35 PM</t>
+  </si>
+  <si>
+    <t>5:32:39 PM</t>
+  </si>
+  <si>
+    <t>1.63s</t>
+  </si>
+  <si>
+    <t>TC_SEL_021</t>
+  </si>
+  <si>
+    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
+  </si>
+  <si>
+    <t>5:32:45 PM</t>
+  </si>
+  <si>
+    <t>5:32:49 PM</t>
+  </si>
+  <si>
+    <t>2.24s</t>
+  </si>
+  <si>
+    <t>TC_SEL_022</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
+  </si>
+  <si>
+    <t>5:32:55 PM</t>
+  </si>
+  <si>
+    <t>5:32:59 PM</t>
+  </si>
+  <si>
+    <t>2.96s</t>
+  </si>
+  <si>
+    <t>TC_SEL_023</t>
+  </si>
+  <si>
+    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
+  </si>
+  <si>
+    <t>5:33:05 PM</t>
+  </si>
+  <si>
+    <t>5:33:09 PM</t>
+  </si>
+  <si>
+    <t>1.81s</t>
+  </si>
+  <si>
+    <t>TC_SEL_024</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
+  </si>
+  <si>
+    <t>5:33:15 PM</t>
+  </si>
+  <si>
+    <t>5:33:19 PM</t>
+  </si>
+  <si>
+    <t>2.66s</t>
+  </si>
+  <si>
+    <t>TC_SEL_025</t>
+  </si>
+  <si>
+    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
+  </si>
+  <si>
+    <t>5:33:25 PM</t>
+  </si>
+  <si>
+    <t>5:33:29 PM</t>
+  </si>
+  <si>
+    <t>2.59s</t>
+  </si>
+  <si>
+    <t>TC_SEL_026</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>TC_SEL_026 - Verify profile details update</t>
+  </si>
+  <si>
+    <t>5:33:35 PM</t>
+  </si>
+  <si>
+    <t>5:33:39 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_027</t>
+  </si>
+  <si>
+    <t>TC_SEL_027 - Verify password update functionality</t>
+  </si>
+  <si>
+    <t>5:33:45 PM</t>
+  </si>
+  <si>
+    <t>5:33:49 PM</t>
+  </si>
+  <si>
+    <t>1.27s</t>
+  </si>
+  <si>
+    <t>TC_SEL_028</t>
+  </si>
+  <si>
+    <t>TC_SEL_028 - Verify currency settings updates</t>
+  </si>
+  <si>
+    <t>5:33:55 PM</t>
+  </si>
+  <si>
+    <t>5:33:59 PM</t>
+  </si>
+  <si>
+    <t>2.87s</t>
+  </si>
+  <si>
+    <t>TC_SEL_029</t>
+  </si>
+  <si>
+    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
+  </si>
+  <si>
+    <t>5:34:05 PM</t>
+  </si>
+  <si>
+    <t>5:34:09 PM</t>
+  </si>
+  <si>
+    <t>2.89s</t>
+  </si>
+  <si>
+    <t>TC_SEL_030</t>
+  </si>
+  <si>
+    <t>TC_SEL_030 - Verify successful user logout and redirection</t>
+  </si>
+  <si>
+    <t>5:34:15 PM</t>
+  </si>
+  <si>
+    <t>5:34:19 PM</t>
   </si>
   <si>
     <t>2.53s</t>
   </si>
   <si>
-    <t>TC_SEL_004</t>
-  </si>
-  <si>
-    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
-  </si>
-  <si>
-    <t>5:22:13 PM</t>
-  </si>
-  <si>
-    <t>5:22:17 PM</t>
-  </si>
-  <si>
-    <t>2.39s</t>
-  </si>
-  <si>
-    <t>TC_SEL_005</t>
-  </si>
-  <si>
-    <t>TC_SEL_005 - Verify login page load</t>
-  </si>
-  <si>
-    <t>5:22:23 PM</t>
-  </si>
-  <si>
-    <t>5:22:27 PM</t>
-  </si>
-  <si>
-    <t>1.86s</t>
-  </si>
-  <si>
-    <t>TC_SEL_006</t>
-  </si>
-  <si>
-    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
-  </si>
-  <si>
-    <t>5:22:33 PM</t>
-  </si>
-  <si>
-    <t>5:22:37 PM</t>
-  </si>
-  <si>
-    <t>2.76s</t>
-  </si>
-  <si>
-    <t>TC_SEL_007</t>
-  </si>
-  <si>
-    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
-  </si>
-  <si>
-    <t>5:22:43 PM</t>
-  </si>
-  <si>
-    <t>5:22:47 PM</t>
-  </si>
-  <si>
-    <t>1.61s</t>
-  </si>
-  <si>
-    <t>TC_SEL_008</t>
-  </si>
-  <si>
-    <t>TC_SEL_008 - Verify forgot password page load</t>
-  </si>
-  <si>
-    <t>5:22:53 PM</t>
-  </si>
-  <si>
-    <t>5:22:57 PM</t>
-  </si>
-  <si>
-    <t>2.96s</t>
-  </si>
-  <si>
-    <t>TC_SEL_009</t>
-  </si>
-  <si>
-    <t>TC_SEL_009 - Verify forgot password email submission</t>
-  </si>
-  <si>
-    <t>5:23:03 PM</t>
-  </si>
-  <si>
-    <t>5:23:07 PM</t>
-  </si>
-  <si>
-    <t>2.33s</t>
-  </si>
-  <si>
-    <t>TC_SEL_010</t>
-  </si>
-  <si>
-    <t>Transactions</t>
-  </si>
-  <si>
-    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
-  </si>
-  <si>
-    <t>5:23:13 PM</t>
-  </si>
-  <si>
-    <t>5:23:17 PM</t>
-  </si>
-  <si>
-    <t>2.63s</t>
-  </si>
-  <si>
-    <t>TC_SEL_011</t>
-  </si>
-  <si>
-    <t>TC_SEL_011 - Verify add income transaction</t>
-  </si>
-  <si>
-    <t>5:23:23 PM</t>
-  </si>
-  <si>
-    <t>5:23:27 PM</t>
-  </si>
-  <si>
-    <t>2.10s</t>
-  </si>
-  <si>
-    <t>TC_SEL_012</t>
-  </si>
-  <si>
-    <t>TC_SEL_012 - Verify add expense transaction</t>
-  </si>
-  <si>
-    <t>5:23:33 PM</t>
-  </si>
-  <si>
-    <t>5:23:37 PM</t>
-  </si>
-  <si>
-    <t>2.80s</t>
-  </si>
-  <si>
-    <t>TC_SEL_013</t>
-  </si>
-  <si>
-    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
-  </si>
-  <si>
-    <t>5:23:43 PM</t>
-  </si>
-  <si>
-    <t>5:23:47 PM</t>
-  </si>
-  <si>
-    <t>1.37s</t>
-  </si>
-  <si>
-    <t>TC_SEL_014</t>
-  </si>
-  <si>
-    <t>TC_SEL_014 - Verify edit transaction title</t>
-  </si>
-  <si>
-    <t>5:23:53 PM</t>
-  </si>
-  <si>
-    <t>5:23:57 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_015</t>
-  </si>
-  <si>
-    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
-  </si>
-  <si>
-    <t>5:24:03 PM</t>
-  </si>
-  <si>
-    <t>5:24:07 PM</t>
-  </si>
-  <si>
-    <t>2.67s</t>
-  </si>
-  <si>
-    <t>TC_SEL_016</t>
-  </si>
-  <si>
-    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
-  </si>
-  <si>
-    <t>5:24:13 PM</t>
-  </si>
-  <si>
-    <t>5:24:17 PM</t>
-  </si>
-  <si>
-    <t>2.13s</t>
-  </si>
-  <si>
-    <t>TC_SEL_017</t>
-  </si>
-  <si>
-    <t>TC_SEL_017 - Verify search transaction by keyword</t>
-  </si>
-  <si>
-    <t>5:24:23 PM</t>
-  </si>
-  <si>
-    <t>5:24:27 PM</t>
-  </si>
-  <si>
-    <t>2.24s</t>
-  </si>
-  <si>
-    <t>TC_SEL_018</t>
-  </si>
-  <si>
-    <t>TC_SEL_018 - Verify filter transactions by category</t>
-  </si>
-  <si>
-    <t>5:24:33 PM</t>
-  </si>
-  <si>
-    <t>5:24:37 PM</t>
-  </si>
-  <si>
-    <t>1.34s</t>
-  </si>
-  <si>
-    <t>TC_SEL_019</t>
-  </si>
-  <si>
-    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
-  </si>
-  <si>
-    <t>5:24:43 PM</t>
-  </si>
-  <si>
-    <t>5:24:47 PM</t>
-  </si>
-  <si>
-    <t>1.79s</t>
-  </si>
-  <si>
-    <t>TC_SEL_020</t>
-  </si>
-  <si>
-    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
-  </si>
-  <si>
-    <t>5:24:53 PM</t>
-  </si>
-  <si>
-    <t>5:24:57 PM</t>
-  </si>
-  <si>
-    <t>1.03s</t>
-  </si>
-  <si>
-    <t>TC_SEL_021</t>
-  </si>
-  <si>
-    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
-  </si>
-  <si>
-    <t>5:25:03 PM</t>
-  </si>
-  <si>
-    <t>5:25:07 PM</t>
-  </si>
-  <si>
-    <t>1.94s</t>
-  </si>
-  <si>
-    <t>TC_SEL_022</t>
-  </si>
-  <si>
-    <t>Budget</t>
-  </si>
-  <si>
-    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
-  </si>
-  <si>
-    <t>5:25:13 PM</t>
-  </si>
-  <si>
-    <t>5:25:17 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_023</t>
-  </si>
-  <si>
-    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
-  </si>
-  <si>
-    <t>5:25:23 PM</t>
-  </si>
-  <si>
-    <t>5:25:27 PM</t>
-  </si>
-  <si>
-    <t>2.79s</t>
-  </si>
-  <si>
-    <t>TC_SEL_024</t>
-  </si>
-  <si>
-    <t>Reports</t>
-  </si>
-  <si>
-    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
-  </si>
-  <si>
-    <t>5:25:33 PM</t>
-  </si>
-  <si>
-    <t>5:25:37 PM</t>
-  </si>
-  <si>
-    <t>1.58s</t>
-  </si>
-  <si>
-    <t>TC_SEL_025</t>
-  </si>
-  <si>
-    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
-  </si>
-  <si>
-    <t>5:25:43 PM</t>
-  </si>
-  <si>
-    <t>5:25:47 PM</t>
-  </si>
-  <si>
-    <t>2.48s</t>
-  </si>
-  <si>
-    <t>TC_SEL_026</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>TC_SEL_026 - Verify profile details update</t>
-  </si>
-  <si>
-    <t>5:25:53 PM</t>
-  </si>
-  <si>
-    <t>5:25:57 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_027</t>
-  </si>
-  <si>
-    <t>TC_SEL_027 - Verify password update functionality</t>
-  </si>
-  <si>
-    <t>5:26:03 PM</t>
-  </si>
-  <si>
-    <t>5:26:07 PM</t>
-  </si>
-  <si>
-    <t>1.88s</t>
-  </si>
-  <si>
-    <t>TC_SEL_028</t>
-  </si>
-  <si>
-    <t>TC_SEL_028 - Verify currency settings updates</t>
-  </si>
-  <si>
-    <t>5:26:13 PM</t>
-  </si>
-  <si>
-    <t>5:26:17 PM</t>
-  </si>
-  <si>
-    <t>2.85s</t>
-  </si>
-  <si>
-    <t>TC_SEL_029</t>
-  </si>
-  <si>
-    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
-  </si>
-  <si>
-    <t>5:26:23 PM</t>
-  </si>
-  <si>
-    <t>5:26:27 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_030</t>
-  </si>
-  <si>
-    <t>TC_SEL_030 - Verify successful user logout and redirection</t>
-  </si>
-  <si>
-    <t>5:26:33 PM</t>
-  </si>
-  <si>
-    <t>5:26:37 PM</t>
-  </si>
-  <si>
-    <t>2.92s</t>
-  </si>
-  <si>
     <t>TC_SEL_031</t>
   </si>
   <si>
     <t>TC_SEL_031 - Verify currency settings updates in layout</t>
   </si>
   <si>
-    <t>5:26:43 PM</t>
-  </si>
-  <si>
-    <t>5:26:47 PM</t>
-  </si>
-  <si>
-    <t>2.38s</t>
+    <t>5:34:25 PM</t>
+  </si>
+  <si>
+    <t>5:34:29 PM</t>
+  </si>
+  <si>
+    <t>1.02s</t>
   </si>
   <si>
     <t>TC_SEL_032</t>
@@ -557,13 +560,10 @@
     <t>TC_SEL_032 - Verify monthly budget limit notifications triggers</t>
   </si>
   <si>
-    <t>5:26:53 PM</t>
-  </si>
-  <si>
-    <t>5:26:57 PM</t>
-  </si>
-  <si>
-    <t>2.78s</t>
+    <t>5:34:35 PM</t>
+  </si>
+  <si>
+    <t>5:34:39 PM</t>
   </si>
   <si>
     <t>TC_SEL_033</t>
@@ -572,10 +572,10 @@
     <t>TC_SEL_033 - Verify monthly PDF report download functionality</t>
   </si>
   <si>
-    <t>5:27:03 PM</t>
-  </si>
-  <si>
-    <t>5:27:07 PM</t>
+    <t>5:34:45 PM</t>
+  </si>
+  <si>
+    <t>5:34:49 PM</t>
   </si>
   <si>
     <t>5.12s</t>
@@ -614,7 +614,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T11:57:13.568Z</t>
+    <t>2026-06-15T12:04:55.240Z</t>
   </si>
   <si>
     <t>Execution of TC_SEL_001</t>
@@ -1552,345 +1552,345 @@
         <v>66</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1898,7 +1898,7 @@
         <v>133</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>134</v>
@@ -1994,7 +1994,7 @@
         <v>153</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -2072,18 +2072,18 @@
         <v>167</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -2092,24 +2092,24 @@
         <v>4</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
@@ -2118,24 +2118,24 @@
         <v>4</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
@@ -2144,13 +2144,13 @@
         <v>4</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -2431,7 +2431,7 @@
         <v>199</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>211</v>
@@ -2448,7 +2448,7 @@
         <v>199</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>212</v>
@@ -2465,7 +2465,7 @@
         <v>199</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>213</v>
@@ -2482,7 +2482,7 @@
         <v>199</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>214</v>
@@ -2499,7 +2499,7 @@
         <v>199</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>215</v>
@@ -2516,7 +2516,7 @@
         <v>199</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>216</v>
@@ -2533,7 +2533,7 @@
         <v>199</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>217</v>
@@ -2550,7 +2550,7 @@
         <v>199</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>218</v>
@@ -2567,7 +2567,7 @@
         <v>199</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>219</v>
@@ -2584,7 +2584,7 @@
         <v>199</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>220</v>
@@ -2601,7 +2601,7 @@
         <v>199</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>221</v>
@@ -2618,7 +2618,7 @@
         <v>199</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>222</v>
@@ -2635,7 +2635,7 @@
         <v>199</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>223</v>
@@ -2771,7 +2771,7 @@
         <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>231</v>
@@ -2788,7 +2788,7 @@
         <v>199</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>232</v>
@@ -2805,7 +2805,7 @@
         <v>199</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>233</v>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="252">
   <si>
     <t>Execution Date</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:34:55 PM</t>
+    <t>6/15/2026, 5:45:32 PM</t>
   </si>
   <si>
     <t>Chrome Web (Headless)</t>
@@ -92,451 +92,454 @@
     <t>TC_SEL_001 - Verify registration page load</t>
   </si>
   <si>
-    <t>5:29:25 PM</t>
-  </si>
-  <si>
-    <t>5:29:29 PM</t>
+    <t>5:40:02 PM</t>
+  </si>
+  <si>
+    <t>5:40:06 PM</t>
+  </si>
+  <si>
+    <t>2.38s</t>
+  </si>
+  <si>
+    <t>TC_SEL_002</t>
+  </si>
+  <si>
+    <t>TC_SEL_002 - Verify successful user registration</t>
+  </si>
+  <si>
+    <t>5:40:12 PM</t>
+  </si>
+  <si>
+    <t>5:40:16 PM</t>
+  </si>
+  <si>
+    <t>1.90s</t>
+  </si>
+  <si>
+    <t>TC_SEL_003</t>
+  </si>
+  <si>
+    <t>TC_SEL_003 - Verify registration validation with existing email</t>
+  </si>
+  <si>
+    <t>5:40:22 PM</t>
+  </si>
+  <si>
+    <t>5:40:26 PM</t>
+  </si>
+  <si>
+    <t>2.31s</t>
+  </si>
+  <si>
+    <t>TC_SEL_004</t>
+  </si>
+  <si>
+    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
+  </si>
+  <si>
+    <t>5:40:32 PM</t>
+  </si>
+  <si>
+    <t>5:40:36 PM</t>
+  </si>
+  <si>
+    <t>2.14s</t>
+  </si>
+  <si>
+    <t>TC_SEL_005</t>
+  </si>
+  <si>
+    <t>TC_SEL_005 - Verify login page load</t>
+  </si>
+  <si>
+    <t>5:40:42 PM</t>
+  </si>
+  <si>
+    <t>5:40:46 PM</t>
+  </si>
+  <si>
+    <t>2.25s</t>
+  </si>
+  <si>
+    <t>TC_SEL_006</t>
+  </si>
+  <si>
+    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
+  </si>
+  <si>
+    <t>5:40:52 PM</t>
+  </si>
+  <si>
+    <t>5:40:56 PM</t>
+  </si>
+  <si>
+    <t>1.32s</t>
+  </si>
+  <si>
+    <t>TC_SEL_007</t>
+  </si>
+  <si>
+    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
+  </si>
+  <si>
+    <t>5:41:02 PM</t>
+  </si>
+  <si>
+    <t>5:41:06 PM</t>
+  </si>
+  <si>
+    <t>1.53s</t>
+  </si>
+  <si>
+    <t>TC_SEL_008</t>
+  </si>
+  <si>
+    <t>TC_SEL_008 - Verify forgot password page load</t>
+  </si>
+  <si>
+    <t>5:41:12 PM</t>
+  </si>
+  <si>
+    <t>5:41:16 PM</t>
+  </si>
+  <si>
+    <t>2.21s</t>
+  </si>
+  <si>
+    <t>TC_SEL_009</t>
+  </si>
+  <si>
+    <t>TC_SEL_009 - Verify forgot password email submission</t>
+  </si>
+  <si>
+    <t>5:41:22 PM</t>
+  </si>
+  <si>
+    <t>5:41:26 PM</t>
+  </si>
+  <si>
+    <t>1.51s</t>
+  </si>
+  <si>
+    <t>TC_SEL_010</t>
+  </si>
+  <si>
+    <t>Transactions</t>
+  </si>
+  <si>
+    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
+  </si>
+  <si>
+    <t>5:41:32 PM</t>
+  </si>
+  <si>
+    <t>5:41:36 PM</t>
+  </si>
+  <si>
+    <t>1.29s</t>
+  </si>
+  <si>
+    <t>TC_SEL_011</t>
+  </si>
+  <si>
+    <t>TC_SEL_011 - Verify add income transaction</t>
+  </si>
+  <si>
+    <t>5:41:42 PM</t>
+  </si>
+  <si>
+    <t>5:41:46 PM</t>
+  </si>
+  <si>
+    <t>2.93s</t>
+  </si>
+  <si>
+    <t>TC_SEL_012</t>
+  </si>
+  <si>
+    <t>TC_SEL_012 - Verify add expense transaction</t>
+  </si>
+  <si>
+    <t>5:41:52 PM</t>
+  </si>
+  <si>
+    <t>5:41:56 PM</t>
+  </si>
+  <si>
+    <t>1.99s</t>
+  </si>
+  <si>
+    <t>TC_SEL_013</t>
+  </si>
+  <si>
+    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
+  </si>
+  <si>
+    <t>5:42:02 PM</t>
+  </si>
+  <si>
+    <t>5:42:06 PM</t>
+  </si>
+  <si>
+    <t>2.64s</t>
+  </si>
+  <si>
+    <t>TC_SEL_014</t>
+  </si>
+  <si>
+    <t>TC_SEL_014 - Verify edit transaction title</t>
+  </si>
+  <si>
+    <t>5:42:12 PM</t>
+  </si>
+  <si>
+    <t>5:42:16 PM</t>
+  </si>
+  <si>
+    <t>2.36s</t>
+  </si>
+  <si>
+    <t>TC_SEL_015</t>
+  </si>
+  <si>
+    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
+  </si>
+  <si>
+    <t>5:42:22 PM</t>
+  </si>
+  <si>
+    <t>5:42:26 PM</t>
+  </si>
+  <si>
+    <t>2.92s</t>
+  </si>
+  <si>
+    <t>TC_SEL_016</t>
+  </si>
+  <si>
+    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
+  </si>
+  <si>
+    <t>5:42:32 PM</t>
+  </si>
+  <si>
+    <t>5:42:36 PM</t>
+  </si>
+  <si>
+    <t>1.96s</t>
+  </si>
+  <si>
+    <t>TC_SEL_017</t>
+  </si>
+  <si>
+    <t>TC_SEL_017 - Verify search transaction by keyword</t>
+  </si>
+  <si>
+    <t>5:42:42 PM</t>
+  </si>
+  <si>
+    <t>5:42:46 PM</t>
+  </si>
+  <si>
+    <t>2.41s</t>
+  </si>
+  <si>
+    <t>TC_SEL_018</t>
+  </si>
+  <si>
+    <t>TC_SEL_018 - Verify filter transactions by category</t>
+  </si>
+  <si>
+    <t>5:42:52 PM</t>
+  </si>
+  <si>
+    <t>5:42:56 PM</t>
+  </si>
+  <si>
+    <t>2.18s</t>
+  </si>
+  <si>
+    <t>TC_SEL_019</t>
+  </si>
+  <si>
+    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
+  </si>
+  <si>
+    <t>5:43:02 PM</t>
+  </si>
+  <si>
+    <t>5:43:06 PM</t>
+  </si>
+  <si>
+    <t>2.60s</t>
+  </si>
+  <si>
+    <t>TC_SEL_020</t>
+  </si>
+  <si>
+    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
+  </si>
+  <si>
+    <t>5:43:12 PM</t>
+  </si>
+  <si>
+    <t>5:43:16 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_021</t>
+  </si>
+  <si>
+    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
+  </si>
+  <si>
+    <t>5:43:22 PM</t>
+  </si>
+  <si>
+    <t>5:43:26 PM</t>
+  </si>
+  <si>
+    <t>1.20s</t>
+  </si>
+  <si>
+    <t>TC_SEL_022</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
+  </si>
+  <si>
+    <t>5:43:32 PM</t>
+  </si>
+  <si>
+    <t>5:43:36 PM</t>
+  </si>
+  <si>
+    <t>1.77s</t>
+  </si>
+  <si>
+    <t>TC_SEL_023</t>
+  </si>
+  <si>
+    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
+  </si>
+  <si>
+    <t>5:43:42 PM</t>
+  </si>
+  <si>
+    <t>5:43:46 PM</t>
+  </si>
+  <si>
+    <t>1.73s</t>
+  </si>
+  <si>
+    <t>TC_SEL_024</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
+  </si>
+  <si>
+    <t>5:43:52 PM</t>
+  </si>
+  <si>
+    <t>5:43:56 PM</t>
+  </si>
+  <si>
+    <t>2.98s</t>
+  </si>
+  <si>
+    <t>TC_SEL_025</t>
+  </si>
+  <si>
+    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
+  </si>
+  <si>
+    <t>5:44:02 PM</t>
+  </si>
+  <si>
+    <t>5:44:06 PM</t>
+  </si>
+  <si>
+    <t>2.39s</t>
+  </si>
+  <si>
+    <t>TC_SEL_026</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>TC_SEL_026 - Verify profile details update</t>
+  </si>
+  <si>
+    <t>5:44:12 PM</t>
+  </si>
+  <si>
+    <t>5:44:16 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_027</t>
+  </si>
+  <si>
+    <t>TC_SEL_027 - Verify password update functionality</t>
+  </si>
+  <si>
+    <t>5:44:22 PM</t>
+  </si>
+  <si>
+    <t>5:44:26 PM</t>
+  </si>
+  <si>
+    <t>1.89s</t>
+  </si>
+  <si>
+    <t>TC_SEL_028</t>
+  </si>
+  <si>
+    <t>TC_SEL_028 - Verify currency settings updates</t>
+  </si>
+  <si>
+    <t>5:44:32 PM</t>
+  </si>
+  <si>
+    <t>5:44:36 PM</t>
+  </si>
+  <si>
+    <t>2.73s</t>
+  </si>
+  <si>
+    <t>TC_SEL_029</t>
+  </si>
+  <si>
+    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
+  </si>
+  <si>
+    <t>5:44:42 PM</t>
+  </si>
+  <si>
+    <t>5:44:46 PM</t>
   </si>
   <si>
     <t>1.37s</t>
   </si>
   <si>
-    <t>TC_SEL_002</t>
-  </si>
-  <si>
-    <t>TC_SEL_002 - Verify successful user registration</t>
-  </si>
-  <si>
-    <t>5:29:35 PM</t>
-  </si>
-  <si>
-    <t>5:29:39 PM</t>
-  </si>
-  <si>
-    <t>2.60s</t>
-  </si>
-  <si>
-    <t>TC_SEL_003</t>
-  </si>
-  <si>
-    <t>TC_SEL_003 - Verify registration validation with existing email</t>
-  </si>
-  <si>
-    <t>5:29:45 PM</t>
-  </si>
-  <si>
-    <t>5:29:49 PM</t>
-  </si>
-  <si>
-    <t>2.76s</t>
-  </si>
-  <si>
-    <t>TC_SEL_004</t>
-  </si>
-  <si>
-    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
-  </si>
-  <si>
-    <t>5:29:55 PM</t>
-  </si>
-  <si>
-    <t>5:29:59 PM</t>
-  </si>
-  <si>
-    <t>1.21s</t>
-  </si>
-  <si>
-    <t>TC_SEL_005</t>
-  </si>
-  <si>
-    <t>TC_SEL_005 - Verify login page load</t>
-  </si>
-  <si>
-    <t>5:30:05 PM</t>
-  </si>
-  <si>
-    <t>5:30:09 PM</t>
-  </si>
-  <si>
-    <t>2.82s</t>
-  </si>
-  <si>
-    <t>TC_SEL_006</t>
-  </si>
-  <si>
-    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
-  </si>
-  <si>
-    <t>5:30:15 PM</t>
-  </si>
-  <si>
-    <t>5:30:19 PM</t>
-  </si>
-  <si>
-    <t>2.10s</t>
-  </si>
-  <si>
-    <t>TC_SEL_007</t>
-  </si>
-  <si>
-    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
-  </si>
-  <si>
-    <t>5:30:25 PM</t>
-  </si>
-  <si>
-    <t>5:30:29 PM</t>
-  </si>
-  <si>
-    <t>2.34s</t>
-  </si>
-  <si>
-    <t>TC_SEL_008</t>
-  </si>
-  <si>
-    <t>TC_SEL_008 - Verify forgot password page load</t>
-  </si>
-  <si>
-    <t>5:30:35 PM</t>
-  </si>
-  <si>
-    <t>5:30:39 PM</t>
-  </si>
-  <si>
-    <t>1.24s</t>
-  </si>
-  <si>
-    <t>TC_SEL_009</t>
-  </si>
-  <si>
-    <t>TC_SEL_009 - Verify forgot password email submission</t>
-  </si>
-  <si>
-    <t>5:30:45 PM</t>
-  </si>
-  <si>
-    <t>5:30:49 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_010</t>
-  </si>
-  <si>
-    <t>Transactions</t>
-  </si>
-  <si>
-    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
-  </si>
-  <si>
-    <t>5:30:55 PM</t>
-  </si>
-  <si>
-    <t>5:30:59 PM</t>
-  </si>
-  <si>
-    <t>1.85s</t>
-  </si>
-  <si>
-    <t>TC_SEL_011</t>
-  </si>
-  <si>
-    <t>TC_SEL_011 - Verify add income transaction</t>
-  </si>
-  <si>
-    <t>5:31:05 PM</t>
-  </si>
-  <si>
-    <t>5:31:09 PM</t>
-  </si>
-  <si>
-    <t>1.23s</t>
-  </si>
-  <si>
-    <t>TC_SEL_012</t>
-  </si>
-  <si>
-    <t>TC_SEL_012 - Verify add expense transaction</t>
-  </si>
-  <si>
-    <t>5:31:15 PM</t>
-  </si>
-  <si>
-    <t>5:31:19 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_013</t>
-  </si>
-  <si>
-    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
-  </si>
-  <si>
-    <t>5:31:25 PM</t>
-  </si>
-  <si>
-    <t>5:31:29 PM</t>
-  </si>
-  <si>
-    <t>1.48s</t>
-  </si>
-  <si>
-    <t>TC_SEL_014</t>
-  </si>
-  <si>
-    <t>TC_SEL_014 - Verify edit transaction title</t>
-  </si>
-  <si>
-    <t>5:31:35 PM</t>
-  </si>
-  <si>
-    <t>5:31:39 PM</t>
-  </si>
-  <si>
-    <t>2.81s</t>
-  </si>
-  <si>
-    <t>TC_SEL_015</t>
-  </si>
-  <si>
-    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
-  </si>
-  <si>
-    <t>5:31:45 PM</t>
-  </si>
-  <si>
-    <t>5:31:49 PM</t>
-  </si>
-  <si>
-    <t>2.72s</t>
-  </si>
-  <si>
-    <t>TC_SEL_016</t>
-  </si>
-  <si>
-    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
-  </si>
-  <si>
-    <t>5:31:55 PM</t>
-  </si>
-  <si>
-    <t>5:31:59 PM</t>
-  </si>
-  <si>
-    <t>1.70s</t>
-  </si>
-  <si>
-    <t>TC_SEL_017</t>
-  </si>
-  <si>
-    <t>TC_SEL_017 - Verify search transaction by keyword</t>
-  </si>
-  <si>
-    <t>5:32:05 PM</t>
-  </si>
-  <si>
-    <t>5:32:09 PM</t>
-  </si>
-  <si>
-    <t>1.16s</t>
-  </si>
-  <si>
-    <t>TC_SEL_018</t>
-  </si>
-  <si>
-    <t>TC_SEL_018 - Verify filter transactions by category</t>
-  </si>
-  <si>
-    <t>5:32:15 PM</t>
-  </si>
-  <si>
-    <t>5:32:19 PM</t>
-  </si>
-  <si>
-    <t>2.27s</t>
-  </si>
-  <si>
-    <t>TC_SEL_019</t>
-  </si>
-  <si>
-    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
-  </si>
-  <si>
-    <t>5:32:25 PM</t>
-  </si>
-  <si>
-    <t>5:32:29 PM</t>
-  </si>
-  <si>
-    <t>2.02s</t>
-  </si>
-  <si>
-    <t>TC_SEL_020</t>
-  </si>
-  <si>
-    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
-  </si>
-  <si>
-    <t>5:32:35 PM</t>
-  </si>
-  <si>
-    <t>5:32:39 PM</t>
-  </si>
-  <si>
-    <t>1.63s</t>
-  </si>
-  <si>
-    <t>TC_SEL_021</t>
-  </si>
-  <si>
-    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
-  </si>
-  <si>
-    <t>5:32:45 PM</t>
-  </si>
-  <si>
-    <t>5:32:49 PM</t>
-  </si>
-  <si>
-    <t>2.24s</t>
-  </si>
-  <si>
-    <t>TC_SEL_022</t>
-  </si>
-  <si>
-    <t>Budget</t>
-  </si>
-  <si>
-    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
-  </si>
-  <si>
-    <t>5:32:55 PM</t>
-  </si>
-  <si>
-    <t>5:32:59 PM</t>
-  </si>
-  <si>
-    <t>2.96s</t>
-  </si>
-  <si>
-    <t>TC_SEL_023</t>
-  </si>
-  <si>
-    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
-  </si>
-  <si>
-    <t>5:33:05 PM</t>
-  </si>
-  <si>
-    <t>5:33:09 PM</t>
-  </si>
-  <si>
-    <t>1.81s</t>
-  </si>
-  <si>
-    <t>TC_SEL_024</t>
-  </si>
-  <si>
-    <t>Reports</t>
-  </si>
-  <si>
-    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
-  </si>
-  <si>
-    <t>5:33:15 PM</t>
-  </si>
-  <si>
-    <t>5:33:19 PM</t>
-  </si>
-  <si>
-    <t>2.66s</t>
-  </si>
-  <si>
-    <t>TC_SEL_025</t>
-  </si>
-  <si>
-    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
-  </si>
-  <si>
-    <t>5:33:25 PM</t>
-  </si>
-  <si>
-    <t>5:33:29 PM</t>
-  </si>
-  <si>
-    <t>2.59s</t>
-  </si>
-  <si>
-    <t>TC_SEL_026</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>TC_SEL_026 - Verify profile details update</t>
-  </si>
-  <si>
-    <t>5:33:35 PM</t>
-  </si>
-  <si>
-    <t>5:33:39 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_027</t>
-  </si>
-  <si>
-    <t>TC_SEL_027 - Verify password update functionality</t>
-  </si>
-  <si>
-    <t>5:33:45 PM</t>
-  </si>
-  <si>
-    <t>5:33:49 PM</t>
-  </si>
-  <si>
-    <t>1.27s</t>
-  </si>
-  <si>
-    <t>TC_SEL_028</t>
-  </si>
-  <si>
-    <t>TC_SEL_028 - Verify currency settings updates</t>
-  </si>
-  <si>
-    <t>5:33:55 PM</t>
-  </si>
-  <si>
-    <t>5:33:59 PM</t>
-  </si>
-  <si>
-    <t>2.87s</t>
-  </si>
-  <si>
-    <t>TC_SEL_029</t>
-  </si>
-  <si>
-    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
-  </si>
-  <si>
-    <t>5:34:05 PM</t>
-  </si>
-  <si>
-    <t>5:34:09 PM</t>
-  </si>
-  <si>
-    <t>2.89s</t>
-  </si>
-  <si>
     <t>TC_SEL_030</t>
   </si>
   <si>
     <t>TC_SEL_030 - Verify successful user logout and redirection</t>
   </si>
   <si>
-    <t>5:34:15 PM</t>
-  </si>
-  <si>
-    <t>5:34:19 PM</t>
-  </si>
-  <si>
-    <t>2.53s</t>
+    <t>5:44:52 PM</t>
+  </si>
+  <si>
+    <t>5:44:56 PM</t>
+  </si>
+  <si>
+    <t>1.57s</t>
   </si>
   <si>
     <t>TC_SEL_031</t>
@@ -545,13 +548,13 @@
     <t>TC_SEL_031 - Verify currency settings updates in layout</t>
   </si>
   <si>
-    <t>5:34:25 PM</t>
-  </si>
-  <si>
-    <t>5:34:29 PM</t>
-  </si>
-  <si>
-    <t>1.02s</t>
+    <t>5:45:02 PM</t>
+  </si>
+  <si>
+    <t>5:45:06 PM</t>
+  </si>
+  <si>
+    <t>1.08s</t>
   </si>
   <si>
     <t>TC_SEL_032</t>
@@ -560,10 +563,13 @@
     <t>TC_SEL_032 - Verify monthly budget limit notifications triggers</t>
   </si>
   <si>
-    <t>5:34:35 PM</t>
-  </si>
-  <si>
-    <t>5:34:39 PM</t>
+    <t>5:45:12 PM</t>
+  </si>
+  <si>
+    <t>5:45:16 PM</t>
+  </si>
+  <si>
+    <t>2.16s</t>
   </si>
   <si>
     <t>TC_SEL_033</t>
@@ -572,10 +578,10 @@
     <t>TC_SEL_033 - Verify monthly PDF report download functionality</t>
   </si>
   <si>
-    <t>5:34:45 PM</t>
-  </si>
-  <si>
-    <t>5:34:49 PM</t>
+    <t>5:45:22 PM</t>
+  </si>
+  <si>
+    <t>5:45:26 PM</t>
   </si>
   <si>
     <t>5.12s</t>
@@ -614,7 +620,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T12:04:55.240Z</t>
+    <t>2026-06-15T12:15:32.203Z</t>
   </si>
   <si>
     <t>Execution of TC_SEL_001</t>
@@ -1552,18 +1558,18 @@
         <v>66</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
@@ -1572,24 +1578,24 @@
         <v>4</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -1598,24 +1604,24 @@
         <v>4</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -1624,24 +1630,24 @@
         <v>4</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -1650,24 +1656,24 @@
         <v>4</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1676,24 +1682,24 @@
         <v>4</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -1702,24 +1708,24 @@
         <v>4</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -1728,24 +1734,24 @@
         <v>4</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -1754,24 +1760,24 @@
         <v>4</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -1780,24 +1786,24 @@
         <v>4</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -1806,24 +1812,24 @@
         <v>4</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -1832,24 +1838,24 @@
         <v>4</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1858,24 +1864,24 @@
         <v>4</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -1884,24 +1890,24 @@
         <v>4</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -1910,24 +1916,24 @@
         <v>4</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1936,24 +1942,24 @@
         <v>4</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -1962,24 +1968,24 @@
         <v>4</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -1988,24 +1994,24 @@
         <v>4</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
@@ -2014,24 +2020,24 @@
         <v>4</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
@@ -2040,24 +2046,24 @@
         <v>4</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
@@ -2066,24 +2072,24 @@
         <v>4</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -2092,24 +2098,24 @@
         <v>4</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
@@ -2118,24 +2124,24 @@
         <v>4</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
@@ -2144,24 +2150,24 @@
         <v>4</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>111</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
@@ -2170,13 +2176,13 @@
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2200,13 +2206,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>17</v>
@@ -2215,18 +2221,18 @@
         <v>2</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>10</v>
@@ -2235,7 +2241,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2258,580 +2264,580 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -2853,70 +2859,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="241">
   <si>
     <t>Execution Date</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:45:32 PM</t>
+    <t>6/15/2026, 6:07:07 PM</t>
   </si>
   <si>
     <t>Chrome Web (Headless)</t>
@@ -53,7 +53,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>96.97%</t>
+    <t>96.77%</t>
   </si>
   <si>
     <t>00:02:15</t>
@@ -92,13 +92,13 @@
     <t>TC_SEL_001 - Verify registration page load</t>
   </si>
   <si>
-    <t>5:40:02 PM</t>
-  </si>
-  <si>
-    <t>5:40:06 PM</t>
-  </si>
-  <si>
-    <t>2.38s</t>
+    <t>6:01:57 PM</t>
+  </si>
+  <si>
+    <t>6:02:01 PM</t>
+  </si>
+  <si>
+    <t>2.23s</t>
   </si>
   <si>
     <t>TC_SEL_002</t>
@@ -107,13 +107,13 @@
     <t>TC_SEL_002 - Verify successful user registration</t>
   </si>
   <si>
-    <t>5:40:12 PM</t>
-  </si>
-  <si>
-    <t>5:40:16 PM</t>
-  </si>
-  <si>
-    <t>1.90s</t>
+    <t>6:02:07 PM</t>
+  </si>
+  <si>
+    <t>6:02:11 PM</t>
+  </si>
+  <si>
+    <t>2.16s</t>
   </si>
   <si>
     <t>TC_SEL_003</t>
@@ -122,13 +122,13 @@
     <t>TC_SEL_003 - Verify registration validation with existing email</t>
   </si>
   <si>
-    <t>5:40:22 PM</t>
-  </si>
-  <si>
-    <t>5:40:26 PM</t>
-  </si>
-  <si>
-    <t>2.31s</t>
+    <t>6:02:17 PM</t>
+  </si>
+  <si>
+    <t>6:02:21 PM</t>
+  </si>
+  <si>
+    <t>2.28s</t>
   </si>
   <si>
     <t>TC_SEL_004</t>
@@ -137,13 +137,13 @@
     <t>TC_SEL_004 - Verify registration invalid password constraints</t>
   </si>
   <si>
-    <t>5:40:32 PM</t>
-  </si>
-  <si>
-    <t>5:40:36 PM</t>
-  </si>
-  <si>
-    <t>2.14s</t>
+    <t>6:02:27 PM</t>
+  </si>
+  <si>
+    <t>6:02:31 PM</t>
+  </si>
+  <si>
+    <t>1.68s</t>
   </si>
   <si>
     <t>TC_SEL_005</t>
@@ -152,13 +152,13 @@
     <t>TC_SEL_005 - Verify login page load</t>
   </si>
   <si>
-    <t>5:40:42 PM</t>
-  </si>
-  <si>
-    <t>5:40:46 PM</t>
-  </si>
-  <si>
-    <t>2.25s</t>
+    <t>6:02:37 PM</t>
+  </si>
+  <si>
+    <t>6:02:41 PM</t>
+  </si>
+  <si>
+    <t>1.52s</t>
   </si>
   <si>
     <t>TC_SEL_006</t>
@@ -167,196 +167,196 @@
     <t>TC_SEL_006 - Verify successful login with valid credentials</t>
   </si>
   <si>
-    <t>5:40:52 PM</t>
-  </si>
-  <si>
-    <t>5:40:56 PM</t>
+    <t>6:02:47 PM</t>
+  </si>
+  <si>
+    <t>6:02:51 PM</t>
+  </si>
+  <si>
+    <t>1.18s</t>
+  </si>
+  <si>
+    <t>TC_SEL_007</t>
+  </si>
+  <si>
+    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
+  </si>
+  <si>
+    <t>6:02:57 PM</t>
+  </si>
+  <si>
+    <t>6:03:01 PM</t>
+  </si>
+  <si>
+    <t>1.62s</t>
+  </si>
+  <si>
+    <t>TC_SEL_008</t>
+  </si>
+  <si>
+    <t>TC_SEL_008 - Verify forgot password page load</t>
+  </si>
+  <si>
+    <t>6:03:07 PM</t>
+  </si>
+  <si>
+    <t>6:03:11 PM</t>
+  </si>
+  <si>
+    <t>1.37s</t>
+  </si>
+  <si>
+    <t>TC_SEL_009</t>
+  </si>
+  <si>
+    <t>TC_SEL_009 - Verify forgot password email submission</t>
+  </si>
+  <si>
+    <t>6:03:17 PM</t>
+  </si>
+  <si>
+    <t>6:03:21 PM</t>
+  </si>
+  <si>
+    <t>2.89s</t>
+  </si>
+  <si>
+    <t>TC_SEL_010</t>
+  </si>
+  <si>
+    <t>Transactions</t>
+  </si>
+  <si>
+    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
+  </si>
+  <si>
+    <t>6:03:27 PM</t>
+  </si>
+  <si>
+    <t>6:03:31 PM</t>
+  </si>
+  <si>
+    <t>2.02s</t>
+  </si>
+  <si>
+    <t>TC_SEL_011</t>
+  </si>
+  <si>
+    <t>TC_SEL_011 - Verify add income transaction</t>
+  </si>
+  <si>
+    <t>6:03:37 PM</t>
+  </si>
+  <si>
+    <t>6:03:41 PM</t>
+  </si>
+  <si>
+    <t>1.59s</t>
+  </si>
+  <si>
+    <t>TC_SEL_012</t>
+  </si>
+  <si>
+    <t>TC_SEL_012 - Verify add expense transaction</t>
+  </si>
+  <si>
+    <t>6:03:47 PM</t>
+  </si>
+  <si>
+    <t>6:03:51 PM</t>
+  </si>
+  <si>
+    <t>1.85s</t>
+  </si>
+  <si>
+    <t>TC_SEL_013</t>
+  </si>
+  <si>
+    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
+  </si>
+  <si>
+    <t>6:03:57 PM</t>
+  </si>
+  <si>
+    <t>6:04:01 PM</t>
+  </si>
+  <si>
+    <t>1.22s</t>
+  </si>
+  <si>
+    <t>TC_SEL_014</t>
+  </si>
+  <si>
+    <t>TC_SEL_014 - Verify edit transaction title</t>
+  </si>
+  <si>
+    <t>6:04:07 PM</t>
+  </si>
+  <si>
+    <t>6:04:11 PM</t>
+  </si>
+  <si>
+    <t>1.63s</t>
+  </si>
+  <si>
+    <t>TC_SEL_015</t>
+  </si>
+  <si>
+    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
+  </si>
+  <si>
+    <t>6:04:17 PM</t>
+  </si>
+  <si>
+    <t>6:04:21 PM</t>
+  </si>
+  <si>
+    <t>1.26s</t>
+  </si>
+  <si>
+    <t>TC_SEL_016</t>
+  </si>
+  <si>
+    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
+  </si>
+  <si>
+    <t>6:04:27 PM</t>
+  </si>
+  <si>
+    <t>6:04:31 PM</t>
+  </si>
+  <si>
+    <t>2.20s</t>
+  </si>
+  <si>
+    <t>TC_SEL_017</t>
+  </si>
+  <si>
+    <t>TC_SEL_017 - Verify search transaction by keyword</t>
+  </si>
+  <si>
+    <t>6:04:37 PM</t>
+  </si>
+  <si>
+    <t>6:04:41 PM</t>
   </si>
   <si>
     <t>1.32s</t>
   </si>
   <si>
-    <t>TC_SEL_007</t>
-  </si>
-  <si>
-    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
-  </si>
-  <si>
-    <t>5:41:02 PM</t>
-  </si>
-  <si>
-    <t>5:41:06 PM</t>
-  </si>
-  <si>
-    <t>1.53s</t>
-  </si>
-  <si>
-    <t>TC_SEL_008</t>
-  </si>
-  <si>
-    <t>TC_SEL_008 - Verify forgot password page load</t>
-  </si>
-  <si>
-    <t>5:41:12 PM</t>
-  </si>
-  <si>
-    <t>5:41:16 PM</t>
-  </si>
-  <si>
-    <t>2.21s</t>
-  </si>
-  <si>
-    <t>TC_SEL_009</t>
-  </si>
-  <si>
-    <t>TC_SEL_009 - Verify forgot password email submission</t>
-  </si>
-  <si>
-    <t>5:41:22 PM</t>
-  </si>
-  <si>
-    <t>5:41:26 PM</t>
-  </si>
-  <si>
-    <t>1.51s</t>
-  </si>
-  <si>
-    <t>TC_SEL_010</t>
-  </si>
-  <si>
-    <t>Transactions</t>
-  </si>
-  <si>
-    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
-  </si>
-  <si>
-    <t>5:41:32 PM</t>
-  </si>
-  <si>
-    <t>5:41:36 PM</t>
-  </si>
-  <si>
-    <t>1.29s</t>
-  </si>
-  <si>
-    <t>TC_SEL_011</t>
-  </si>
-  <si>
-    <t>TC_SEL_011 - Verify add income transaction</t>
-  </si>
-  <si>
-    <t>5:41:42 PM</t>
-  </si>
-  <si>
-    <t>5:41:46 PM</t>
-  </si>
-  <si>
-    <t>2.93s</t>
-  </si>
-  <si>
-    <t>TC_SEL_012</t>
-  </si>
-  <si>
-    <t>TC_SEL_012 - Verify add expense transaction</t>
-  </si>
-  <si>
-    <t>5:41:52 PM</t>
-  </si>
-  <si>
-    <t>5:41:56 PM</t>
-  </si>
-  <si>
-    <t>1.99s</t>
-  </si>
-  <si>
-    <t>TC_SEL_013</t>
-  </si>
-  <si>
-    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
-  </si>
-  <si>
-    <t>5:42:02 PM</t>
-  </si>
-  <si>
-    <t>5:42:06 PM</t>
-  </si>
-  <si>
-    <t>2.64s</t>
-  </si>
-  <si>
-    <t>TC_SEL_014</t>
-  </si>
-  <si>
-    <t>TC_SEL_014 - Verify edit transaction title</t>
-  </si>
-  <si>
-    <t>5:42:12 PM</t>
-  </si>
-  <si>
-    <t>5:42:16 PM</t>
-  </si>
-  <si>
-    <t>2.36s</t>
-  </si>
-  <si>
-    <t>TC_SEL_015</t>
-  </si>
-  <si>
-    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
-  </si>
-  <si>
-    <t>5:42:22 PM</t>
-  </si>
-  <si>
-    <t>5:42:26 PM</t>
-  </si>
-  <si>
-    <t>2.92s</t>
-  </si>
-  <si>
-    <t>TC_SEL_016</t>
-  </si>
-  <si>
-    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
-  </si>
-  <si>
-    <t>5:42:32 PM</t>
-  </si>
-  <si>
-    <t>5:42:36 PM</t>
-  </si>
-  <si>
-    <t>1.96s</t>
-  </si>
-  <si>
-    <t>TC_SEL_017</t>
-  </si>
-  <si>
-    <t>TC_SEL_017 - Verify search transaction by keyword</t>
-  </si>
-  <si>
-    <t>5:42:42 PM</t>
-  </si>
-  <si>
-    <t>5:42:46 PM</t>
-  </si>
-  <si>
-    <t>2.41s</t>
-  </si>
-  <si>
     <t>TC_SEL_018</t>
   </si>
   <si>
     <t>TC_SEL_018 - Verify filter transactions by category</t>
   </si>
   <si>
-    <t>5:42:52 PM</t>
-  </si>
-  <si>
-    <t>5:42:56 PM</t>
-  </si>
-  <si>
-    <t>2.18s</t>
+    <t>6:04:47 PM</t>
+  </si>
+  <si>
+    <t>6:04:51 PM</t>
+  </si>
+  <si>
+    <t>2.80s</t>
   </si>
   <si>
     <t>TC_SEL_019</t>
@@ -365,13 +365,13 @@
     <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
   </si>
   <si>
-    <t>5:43:02 PM</t>
-  </si>
-  <si>
-    <t>5:43:06 PM</t>
-  </si>
-  <si>
-    <t>2.60s</t>
+    <t>6:04:57 PM</t>
+  </si>
+  <si>
+    <t>6:05:01 PM</t>
+  </si>
+  <si>
+    <t>1.12s</t>
   </si>
   <si>
     <t>TC_SEL_020</t>
@@ -380,10 +380,13 @@
     <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
   </si>
   <si>
-    <t>5:43:12 PM</t>
-  </si>
-  <si>
-    <t>5:43:16 PM</t>
+    <t>6:05:07 PM</t>
+  </si>
+  <si>
+    <t>6:05:11 PM</t>
+  </si>
+  <si>
+    <t>2.29s</t>
   </si>
   <si>
     <t>TC_SEL_021</t>
@@ -392,13 +395,13 @@
     <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
   </si>
   <si>
-    <t>5:43:22 PM</t>
-  </si>
-  <si>
-    <t>5:43:26 PM</t>
-  </si>
-  <si>
-    <t>1.20s</t>
+    <t>6:05:17 PM</t>
+  </si>
+  <si>
+    <t>6:05:21 PM</t>
+  </si>
+  <si>
+    <t>2.81s</t>
   </si>
   <si>
     <t>TC_SEL_022</t>
@@ -410,13 +413,13 @@
     <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
   </si>
   <si>
-    <t>5:43:32 PM</t>
-  </si>
-  <si>
-    <t>5:43:36 PM</t>
-  </si>
-  <si>
-    <t>1.77s</t>
+    <t>6:05:27 PM</t>
+  </si>
+  <si>
+    <t>6:05:31 PM</t>
+  </si>
+  <si>
+    <t>1.66s</t>
   </si>
   <si>
     <t>TC_SEL_023</t>
@@ -425,13 +428,13 @@
     <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
   </si>
   <si>
-    <t>5:43:42 PM</t>
-  </si>
-  <si>
-    <t>5:43:46 PM</t>
-  </si>
-  <si>
-    <t>1.73s</t>
+    <t>6:05:37 PM</t>
+  </si>
+  <si>
+    <t>6:05:41 PM</t>
+  </si>
+  <si>
+    <t>1.84s</t>
   </si>
   <si>
     <t>TC_SEL_024</t>
@@ -443,13 +446,13 @@
     <t>TC_SEL_024 - Verify monthly PDF report generation</t>
   </si>
   <si>
-    <t>5:43:52 PM</t>
-  </si>
-  <si>
-    <t>5:43:56 PM</t>
-  </si>
-  <si>
-    <t>2.98s</t>
+    <t>6:05:47 PM</t>
+  </si>
+  <si>
+    <t>6:05:51 PM</t>
+  </si>
+  <si>
+    <t>1.50s</t>
   </si>
   <si>
     <t>TC_SEL_025</t>
@@ -458,13 +461,13 @@
     <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
   </si>
   <si>
-    <t>5:44:02 PM</t>
-  </si>
-  <si>
-    <t>5:44:06 PM</t>
-  </si>
-  <si>
-    <t>2.39s</t>
+    <t>6:05:57 PM</t>
+  </si>
+  <si>
+    <t>6:06:01 PM</t>
+  </si>
+  <si>
+    <t>2.65s</t>
   </si>
   <si>
     <t>TC_SEL_026</t>
@@ -476,10 +479,13 @@
     <t>TC_SEL_026 - Verify profile details update</t>
   </si>
   <si>
-    <t>5:44:12 PM</t>
-  </si>
-  <si>
-    <t>5:44:16 PM</t>
+    <t>6:06:07 PM</t>
+  </si>
+  <si>
+    <t>6:06:11 PM</t>
+  </si>
+  <si>
+    <t>1.55s</t>
   </si>
   <si>
     <t>TC_SEL_027</t>
@@ -488,13 +494,13 @@
     <t>TC_SEL_027 - Verify password update functionality</t>
   </si>
   <si>
-    <t>5:44:22 PM</t>
-  </si>
-  <si>
-    <t>5:44:26 PM</t>
-  </si>
-  <si>
-    <t>1.89s</t>
+    <t>6:06:17 PM</t>
+  </si>
+  <si>
+    <t>6:06:21 PM</t>
+  </si>
+  <si>
+    <t>1.74s</t>
   </si>
   <si>
     <t>TC_SEL_028</t>
@@ -503,13 +509,13 @@
     <t>TC_SEL_028 - Verify currency settings updates</t>
   </si>
   <si>
-    <t>5:44:32 PM</t>
-  </si>
-  <si>
-    <t>5:44:36 PM</t>
-  </si>
-  <si>
-    <t>2.73s</t>
+    <t>6:06:27 PM</t>
+  </si>
+  <si>
+    <t>6:06:31 PM</t>
+  </si>
+  <si>
+    <t>2.47s</t>
   </si>
   <si>
     <t>TC_SEL_029</t>
@@ -518,13 +524,10 @@
     <t>TC_SEL_029 - Verify session persistence on page refresh</t>
   </si>
   <si>
-    <t>5:44:42 PM</t>
-  </si>
-  <si>
-    <t>5:44:46 PM</t>
-  </si>
-  <si>
-    <t>1.37s</t>
+    <t>6:06:37 PM</t>
+  </si>
+  <si>
+    <t>6:06:41 PM</t>
   </si>
   <si>
     <t>TC_SEL_030</t>
@@ -533,55 +536,25 @@
     <t>TC_SEL_030 - Verify successful user logout and redirection</t>
   </si>
   <si>
-    <t>5:44:52 PM</t>
-  </si>
-  <si>
-    <t>5:44:56 PM</t>
-  </si>
-  <si>
-    <t>1.57s</t>
+    <t>6:06:47 PM</t>
+  </si>
+  <si>
+    <t>6:06:51 PM</t>
+  </si>
+  <si>
+    <t>1.64s</t>
   </si>
   <si>
     <t>TC_SEL_031</t>
   </si>
   <si>
-    <t>TC_SEL_031 - Verify currency settings updates in layout</t>
-  </si>
-  <si>
-    <t>5:45:02 PM</t>
-  </si>
-  <si>
-    <t>5:45:06 PM</t>
-  </si>
-  <si>
-    <t>1.08s</t>
-  </si>
-  <si>
-    <t>TC_SEL_032</t>
-  </si>
-  <si>
-    <t>TC_SEL_032 - Verify monthly budget limit notifications triggers</t>
-  </si>
-  <si>
-    <t>5:45:12 PM</t>
-  </si>
-  <si>
-    <t>5:45:16 PM</t>
-  </si>
-  <si>
-    <t>2.16s</t>
-  </si>
-  <si>
-    <t>TC_SEL_033</t>
-  </si>
-  <si>
-    <t>TC_SEL_033 - Verify monthly PDF report download functionality</t>
-  </si>
-  <si>
-    <t>5:45:22 PM</t>
-  </si>
-  <si>
-    <t>5:45:26 PM</t>
+    <t>TC_SEL_031 - Verify monthly PDF report download functionality</t>
+  </si>
+  <si>
+    <t>6:06:57 PM</t>
+  </si>
+  <si>
+    <t>6:07:01 PM</t>
   </si>
   <si>
     <t>5.12s</t>
@@ -620,7 +593,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T12:15:32.203Z</t>
+    <t>2026-06-15T12:37:07.269Z</t>
   </si>
   <si>
     <t>Execution of TC_SEL_001</t>
@@ -720,12 +693,6 @@
   </si>
   <si>
     <t>Execution of TC_SEL_031</t>
-  </si>
-  <si>
-    <t>Execution of TC_SEL_032</t>
-  </si>
-  <si>
-    <t>Execution of TC_SEL_033</t>
   </si>
   <si>
     <t>FAILED</t>
@@ -1263,10 +1230,10 @@
         <v>11</v>
       </c>
       <c r="D2" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -1289,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1844,18 +1811,18 @@
         <v>122</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1864,24 +1831,24 @@
         <v>4</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -1890,24 +1857,24 @@
         <v>4</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -1916,24 +1883,24 @@
         <v>4</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -1942,24 +1909,24 @@
         <v>4</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -1968,24 +1935,24 @@
         <v>4</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -1994,24 +1961,24 @@
         <v>4</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
@@ -2020,24 +1987,24 @@
         <v>4</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
@@ -2046,24 +2013,24 @@
         <v>4</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
@@ -2072,24 +2039,24 @@
         <v>4</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -2098,91 +2065,39 @@
         <v>4</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>4</v>
+      <c r="E32" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2206,13 +2121,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>17</v>
@@ -2221,18 +2136,18 @@
         <v>2</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>186</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>195</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>10</v>
@@ -2241,7 +2156,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2252,7 +2167,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -2264,580 +2179,546 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>114</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>119</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>203</v>
+        <v>225</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>226</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2859,70 +2740,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
